--- a/output_data/AC_Storage_OG.xlsx
+++ b/output_data/AC_Storage_OG.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1325.210573987122</v>
+        <v>502.3661138860319</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1212.672787719406</v>
+        <v>391.1869694104215</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1137.260166613583</v>
+        <v>317.2238244027906</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1054.62811491703</v>
+        <v>235.6173934972684</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>955.9345091728396</v>
+        <v>138.2492234723801</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>903.4985345063947</v>
+        <v>125.591528471508</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1048.736320445842</v>
+        <v>238.6239040958652</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1198.2304514857</v>
+        <v>351.6562797202224</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1368.067251526571</v>
+        <v>464.6886553445796</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1612.435305446677</v>
+        <v>577.7210309689368</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1876.092011264238</v>
+        <v>690.753406593294</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2139.748717081799</v>
+        <v>803.7857822176512</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2403.405422899359</v>
+        <v>916.8181578420084</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2613.250894647982</v>
+        <v>1029.850533466366</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2634.235441822844</v>
+        <v>1120.276433965851</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2636.33389654033</v>
+        <v>1129.3190240158</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2566.543534155626</v>
+        <v>1066.835001162189</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2354.630093727822</v>
+        <v>941.2434726906807</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2061.678198374977</v>
+        <v>815.6519442191727</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1768.726303022132</v>
+        <v>690.0604157476647</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>1475.774407669287</v>
+        <v>564.4688872761567</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>1182.822512316442</v>
+        <v>438.8773588046487</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>917.7917246701672</v>
+        <v>313.2858303331407</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>696.7467005385046</v>
+        <v>187.6943018616327</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2929.518953528451</v>
+        <v>1255.91528471508</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/AC_Storage_OG.xlsx
+++ b/output_data/AC_Storage_OG.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>502.3661138860319</v>
+        <v>559.1997668752623</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>391.1869694104215</v>
+        <v>446.9626873135784</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>317.2238244027906</v>
+        <v>372.3951775041244</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>235.6173934972684</v>
+        <v>292.3816493396995</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>138.2492234723801</v>
+        <v>194.1405701190049</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>125.591528471508</v>
+        <v>140.9676817730152</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>238.6239040958652</v>
+        <v>266.7876293199492</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>351.6562797202224</v>
+        <v>392.6075768668832</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>464.6886553445796</v>
+        <v>518.4275244138172</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>577.7210309689368</v>
+        <v>644.2474719607512</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>690.753406593294</v>
+        <v>770.0674195076853</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>803.7857822176512</v>
+        <v>895.8873670546193</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>916.8181578420084</v>
+        <v>1021.707314601553</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1029.850533466366</v>
+        <v>1147.527262148487</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1120.276433965851</v>
+        <v>1247.132254137255</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1129.3190240158</v>
+        <v>1257.092753336132</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1066.835001162189</v>
+        <v>1205.02349196864</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>941.2434726906807</v>
+        <v>1065.223550249825</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>815.6519442191727</v>
+        <v>925.4236085310091</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>690.0604157476647</v>
+        <v>785.6236668121935</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>564.4688872761567</v>
+        <v>645.8237250933779</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>438.8773588046487</v>
+        <v>506.0237833745623</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>313.2858303331407</v>
+        <v>366.2238416557467</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>187.6943018616327</v>
+        <v>226.4238999369311</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1255.91528471508</v>
+        <v>1397.999417188156</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/AC_Storage_OG.xlsx
+++ b/output_data/AC_Storage_OG.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>559.1997668752623</v>
+        <v>505.9307084585372</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>446.9626873135784</v>
+        <v>393.6936288968533</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>372.3951775041244</v>
+        <v>319.1261190873993</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>292.3816493396995</v>
+        <v>239.1125909229744</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>194.1405701190049</v>
+        <v>140.8715117022798</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>140.9676817730152</v>
+        <v>126.4826771146343</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>266.7876293199492</v>
+        <v>240.3170865178052</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>392.6075768668832</v>
+        <v>354.151495920976</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>518.4275244138172</v>
+        <v>467.9859053241469</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>644.2474719607512</v>
+        <v>581.8203147273177</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>770.0674195076853</v>
+        <v>695.6547241304886</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>895.8873670546193</v>
+        <v>809.4891335336595</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1021.707314601553</v>
+        <v>923.3235429368303</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1147.527262148487</v>
+        <v>1037.157952340001</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1247.132254137255</v>
+        <v>1128.225479862538</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1257.092753336132</v>
+        <v>1137.332232614792</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1205.02349196864</v>
+        <v>1097.21066774381</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1065.223550249825</v>
+        <v>970.7279906291756</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>925.4236085310091</v>
+        <v>844.2453135145413</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>785.6236668121935</v>
+        <v>717.762636399907</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>645.8237250933779</v>
+        <v>591.2799592852728</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>506.0237833745623</v>
+        <v>464.7972821706385</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>366.2238416557467</v>
+        <v>338.3146050560042</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>226.4238999369311</v>
+        <v>211.8319279413699</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1397.999417188156</v>
+        <v>1264.826771146343</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/AC_Storage_OG.xlsx
+++ b/output_data/AC_Storage_OG.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>505.9307084585372</v>
+        <v>505.668059729497</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>393.6936288968533</v>
+        <v>393.4309801678131</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>319.1261190873993</v>
+        <v>318.8634703583591</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>239.1125909229744</v>
+        <v>238.8499421939342</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>140.8715117022798</v>
+        <v>140.6088629732396</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>126.4826771146343</v>
+        <v>126.4170149323742</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>240.3170865178052</v>
+        <v>240.1923283715111</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>354.151495920976</v>
+        <v>353.9676418106479</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>467.9859053241469</v>
+        <v>467.7429552497847</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>581.8203147273177</v>
+        <v>581.5182686889216</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>695.6547241304886</v>
+        <v>695.2935821280585</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>809.4891335336595</v>
+        <v>809.0688955671953</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>923.3235429368303</v>
+        <v>922.8442090063322</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1037.157952340001</v>
+        <v>1036.619522445469</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1128.225479862538</v>
+        <v>1127.639773196778</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1137.332232614792</v>
+        <v>1136.741798271909</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1097.21066774381</v>
+        <v>1121.447919124359</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>970.7279906291756</v>
+        <v>995.0309041919847</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>844.2453135145413</v>
+        <v>868.6138892596105</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>717.762636399907</v>
+        <v>742.1968743272362</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>591.2799592852728</v>
+        <v>615.7798593948619</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>464.7972821706385</v>
+        <v>489.3628444624877</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>338.3146050560042</v>
+        <v>362.9458295301134</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>211.8319279413699</v>
+        <v>236.5288145977392</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1264.826771146343</v>
+        <v>1264.170149323742</v>
       </c>
     </row>
   </sheetData>
